--- a/etl/data/inputs/Shell White Oil Tank Cleaning Guide - cleaning process.xlsx
+++ b/etl/data/inputs/Shell White Oil Tank Cleaning Guide - cleaning process.xlsx
@@ -1,114 +1,144 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="24">
   <si>
-    <t>id</t>
+    <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t>grade_to_be_loaded</t>
+    <t xml:space="preserve">grade_to_be_loaded</t>
   </si>
   <si>
-    <t>grade_discharged_previous_cargo</t>
+    <t xml:space="preserve">grade_discharged_previous_cargo</t>
   </si>
   <si>
-    <t>procedure_code</t>
+    <t xml:space="preserve">procedure_code</t>
   </si>
   <si>
-    <t>compatibility_status</t>
+    <t xml:space="preserve">compatibility_status</t>
   </si>
   <si>
-    <t>Avgas</t>
+    <t xml:space="preserve">Avgas</t>
   </si>
   <si>
-    <t>COMPATIBLE</t>
+    <t xml:space="preserve">COMPATIBLE</t>
   </si>
   <si>
-    <t>Avtag</t>
+    <t xml:space="preserve">Avtag</t>
   </si>
   <si>
-    <t>Avtur</t>
+    <t xml:space="preserve">Avtur</t>
   </si>
   <si>
-    <t>Mogas (Unleaded)</t>
+    <t xml:space="preserve">Mogas (Unleaded)</t>
   </si>
   <si>
-    <t>Mogas</t>
+    <t xml:space="preserve">Mogas</t>
   </si>
   <si>
-    <t>Mogas (Military)</t>
+    <t xml:space="preserve">Mogas (Military)</t>
   </si>
   <si>
-    <t>Mogas Component</t>
+    <t xml:space="preserve">Mogas Component</t>
   </si>
   <si>
-    <t>Naphtha</t>
+    <t xml:space="preserve">Naphtha</t>
   </si>
   <si>
-    <t>CONDITIONAL</t>
+    <t xml:space="preserve">CONDITIONAL</t>
   </si>
   <si>
-    <t>Naphtha (Lead Free)</t>
+    <t xml:space="preserve">Naphtha (Lead Free)</t>
   </si>
   <si>
-    <t>Platformer Feedstock</t>
+    <t xml:space="preserve">Platformer Feedstock</t>
   </si>
   <si>
-    <t>Natural Gasoline</t>
+    <t xml:space="preserve">Natural Gasoline</t>
   </si>
   <si>
-    <t>Kerosine</t>
+    <t xml:space="preserve">Kerosine</t>
   </si>
   <si>
-    <t>Gasoil</t>
+    <t xml:space="preserve">Gasoil</t>
   </si>
   <si>
-    <t>SBP</t>
+    <t xml:space="preserve">SBP</t>
   </si>
   <si>
-    <t>White Spirit</t>
+    <t xml:space="preserve">White Spirit</t>
   </si>
   <si>
-    <t>Lub. Oil</t>
+    <t xml:space="preserve">Lub. Oil</t>
   </si>
   <si>
-    <t>INCOMPATIBLE</t>
+    <t xml:space="preserve">INCOMPATIBLE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="m/d"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -116,258 +146,153 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF1F4E78"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
-  <a:themeElements>
-    <a:clrScheme name="Sheets">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4285F4"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="EA4335"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="FBBC04"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="34A853"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="FF6D01"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="46BDC6"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="1155CC"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="1155CC"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Sheets">
-      <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E257"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="33.25"/>
-    <col customWidth="1" min="3" max="3" width="36.25"/>
-    <col customWidth="1" min="4" max="4" width="29.25"/>
-    <col customWidth="1" min="5" max="5" width="20.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="54.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.37"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -384,9 +309,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -394,16 +319,16 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
-        <v>1.0</v>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>2.0</v>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -411,16 +336,16 @@
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2">
-        <v>2.0</v>
+      <c r="D3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>3.0</v>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -428,16 +353,16 @@
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2">
-        <v>2.0</v>
+      <c r="D4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>4.0</v>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -445,16 +370,16 @@
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2">
-        <v>1.0</v>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>5.0</v>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -462,16 +387,16 @@
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="2">
-        <v>1.0</v>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>6.0</v>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -479,16 +404,16 @@
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="2">
-        <v>1.0</v>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>7.0</v>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -496,16 +421,16 @@
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="2">
-        <v>2.0</v>
+      <c r="D8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>8.0</v>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -513,16 +438,16 @@
       <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="2">
-        <v>2.0</v>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>9.0</v>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -530,16 +455,16 @@
       <c r="C10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2">
-        <v>2.0</v>
+      <c r="D10" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>10.0</v>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -547,16 +472,16 @@
       <c r="C11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="2">
-        <v>1.0</v>
+      <c r="D11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>11.0</v>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -564,16 +489,16 @@
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="2">
-        <v>2.0</v>
+      <c r="D12" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <v>12.0</v>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -581,16 +506,16 @@
       <c r="C13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="2">
-        <v>2.0</v>
+      <c r="D13" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>13.0</v>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -598,16 +523,16 @@
       <c r="C14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="2">
-        <v>2.0</v>
+      <c r="D14" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2">
-        <v>14.0</v>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -615,16 +540,16 @@
       <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="2">
-        <v>2.0</v>
+      <c r="D15" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2">
-        <v>15.0</v>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -632,16 +557,16 @@
       <c r="C16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="2">
-        <v>2.0</v>
+      <c r="D16" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2">
-        <v>16.0</v>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -649,16 +574,16 @@
       <c r="C17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="2">
-        <v>5.0</v>
+      <c r="D17" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2">
-        <v>17.0</v>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
@@ -666,16 +591,16 @@
       <c r="C18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2">
-        <v>5.0</v>
+      <c r="D18" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2">
-        <v>18.0</v>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>7</v>
@@ -683,16 +608,16 @@
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="2">
-        <v>1.0</v>
+      <c r="D19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2">
-        <v>19.0</v>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>7</v>
@@ -700,16 +625,16 @@
       <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="2">
-        <v>1.0</v>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2">
-        <v>20.0</v>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>7</v>
@@ -717,16 +642,16 @@
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="2">
-        <v>4.0</v>
+      <c r="D21" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2">
-        <v>21.0</v>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
@@ -734,16 +659,16 @@
       <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="2">
-        <v>5.0</v>
+      <c r="D22" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2">
-        <v>22.0</v>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>7</v>
@@ -751,16 +676,16 @@
       <c r="C23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="2">
-        <v>5.0</v>
+      <c r="D23" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2">
-        <v>23.0</v>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
@@ -768,16 +693,16 @@
       <c r="C24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="2">
-        <v>4.0</v>
+      <c r="D24" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2">
-        <v>24.0</v>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>7</v>
@@ -785,16 +710,16 @@
       <c r="C25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="2">
-        <v>4.0</v>
+      <c r="D25" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2">
-        <v>25.0</v>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>7</v>
@@ -802,16 +727,16 @@
       <c r="C26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="2">
-        <v>4.0</v>
+      <c r="D26" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2">
-        <v>26.0</v>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>7</v>
@@ -819,16 +744,16 @@
       <c r="C27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="2">
-        <v>1.0</v>
+      <c r="D27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2">
-        <v>27.0</v>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
@@ -836,16 +761,16 @@
       <c r="C28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="2">
-        <v>4.0</v>
+      <c r="D28" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2">
-        <v>28.0</v>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>7</v>
@@ -853,16 +778,16 @@
       <c r="C29" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="2">
-        <v>1.0</v>
+      <c r="D29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2">
-        <v>29.0</v>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>7</v>
@@ -870,16 +795,16 @@
       <c r="C30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="2">
-        <v>4.0</v>
+      <c r="D30" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2">
-        <v>30.0</v>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>7</v>
@@ -887,16 +812,16 @@
       <c r="C31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="2">
-        <v>1.0</v>
+      <c r="D31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2">
-        <v>31.0</v>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>7</v>
@@ -904,16 +829,16 @@
       <c r="C32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="2">
-        <v>1.0</v>
+      <c r="D32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2">
-        <v>32.0</v>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>7</v>
@@ -921,16 +846,16 @@
       <c r="C33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="2">
-        <v>5.0</v>
+      <c r="D33" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <v>33.0</v>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>8</v>
@@ -938,16 +863,16 @@
       <c r="C34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="2">
-        <v>5.0</v>
+      <c r="D34" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2">
-        <v>34.0</v>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>8</v>
@@ -955,16 +880,16 @@
       <c r="C35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="2">
-        <v>4.0</v>
+      <c r="D35" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2">
-        <v>35.0</v>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>8</v>
@@ -972,16 +897,16 @@
       <c r="C36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="2">
-        <v>1.0</v>
+      <c r="D36" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2">
-        <v>36.0</v>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>8</v>
@@ -989,16 +914,16 @@
       <c r="C37" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="2">
-        <v>4.0</v>
+      <c r="D37" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2">
-        <v>37.0</v>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>8</v>
@@ -1006,16 +931,16 @@
       <c r="C38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="2">
-        <v>5.0</v>
+      <c r="D38" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2">
-        <v>38.0</v>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>8</v>
@@ -1023,16 +948,16 @@
       <c r="C39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="2">
-        <v>5.0</v>
+      <c r="D39" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2">
-        <v>39.0</v>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>8</v>
@@ -1040,16 +965,16 @@
       <c r="C40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="2">
-        <v>4.0</v>
+      <c r="D40" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2">
-        <v>40.0</v>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>8</v>
@@ -1057,16 +982,16 @@
       <c r="C41" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="2">
-        <v>4.0</v>
+      <c r="D41" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2">
-        <v>41.0</v>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>8</v>
@@ -1074,16 +999,16 @@
       <c r="C42" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="2">
-        <v>4.0</v>
+      <c r="D42" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2">
-        <v>42.0</v>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>8</v>
@@ -1091,16 +1016,16 @@
       <c r="C43" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D43" s="2">
-        <v>4.0</v>
+      <c r="D43" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2">
-        <v>43.0</v>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>8</v>
@@ -1108,16 +1033,16 @@
       <c r="C44" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="2">
-        <v>4.0</v>
+      <c r="D44" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2">
-        <v>44.0</v>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>8</v>
@@ -1125,16 +1050,16 @@
       <c r="C45" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="2">
-        <v>1.0</v>
+      <c r="D45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2">
-        <v>45.0</v>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>8</v>
@@ -1142,16 +1067,16 @@
       <c r="C46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="2">
-        <v>1.0</v>
+      <c r="D46" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2">
-        <v>46.0</v>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>8</v>
@@ -1159,16 +1084,16 @@
       <c r="C47" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="2">
-        <v>4.0</v>
+      <c r="D47" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2">
-        <v>47.0</v>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>8</v>
@@ -1176,16 +1101,16 @@
       <c r="C48" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="2">
-        <v>4.0</v>
+      <c r="D48" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2">
-        <v>48.0</v>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>8</v>
@@ -1193,16 +1118,16 @@
       <c r="C49" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D49" s="2">
-        <v>6.0</v>
+      <c r="D49" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2">
-        <v>49.0</v>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>9</v>
@@ -1210,16 +1135,16 @@
       <c r="C50" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="2">
-        <v>1.0</v>
+      <c r="D50" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2">
-        <v>50.0</v>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>9</v>
@@ -1227,16 +1152,16 @@
       <c r="C51" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D51" s="2">
-        <v>1.0</v>
+      <c r="D51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2">
-        <v>51.0</v>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>9</v>
@@ -1244,16 +1169,16 @@
       <c r="C52" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="2">
-        <v>1.0</v>
+      <c r="D52" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2">
-        <v>52.0</v>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>9</v>
@@ -1261,16 +1186,16 @@
       <c r="C53" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D53" s="2">
-        <v>1.0</v>
+      <c r="D53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2">
-        <v>53.0</v>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>9</v>
@@ -1278,16 +1203,16 @@
       <c r="C54" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="2">
-        <v>1.0</v>
+      <c r="D54" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2">
-        <v>54.0</v>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>9</v>
@@ -1295,16 +1220,16 @@
       <c r="C55" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D55" s="2">
-        <v>1.0</v>
+      <c r="D55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2">
-        <v>55.0</v>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>9</v>
@@ -1312,16 +1237,16 @@
       <c r="C56" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="2">
-        <v>1.0</v>
+      <c r="D56" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2">
-        <v>56.0</v>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>9</v>
@@ -1329,16 +1254,16 @@
       <c r="C57" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D57" s="2">
-        <v>1.0</v>
+      <c r="D57" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2">
-        <v>57.0</v>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>9</v>
@@ -1346,16 +1271,16 @@
       <c r="C58" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D58" s="2">
-        <v>1.0</v>
+      <c r="D58" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2">
-        <v>58.0</v>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>9</v>
@@ -1363,16 +1288,16 @@
       <c r="C59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="2">
-        <v>1.0</v>
+      <c r="D59" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2">
-        <v>59.0</v>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>9</v>
@@ -1380,16 +1305,16 @@
       <c r="C60" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="2">
-        <v>1.0</v>
+      <c r="D60" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2">
-        <v>60.0</v>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>9</v>
@@ -1397,16 +1322,16 @@
       <c r="C61" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="2">
-        <v>1.0</v>
+      <c r="D61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2">
-        <v>61.0</v>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>9</v>
@@ -1414,16 +1339,16 @@
       <c r="C62" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D62" s="2">
-        <v>2.0</v>
+      <c r="D62" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2">
-        <v>62.0</v>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>9</v>
@@ -1431,16 +1356,16 @@
       <c r="C63" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D63" s="2">
-        <v>1.0</v>
+      <c r="D63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2">
-        <v>63.0</v>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>9</v>
@@ -1448,16 +1373,16 @@
       <c r="C64" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="2">
-        <v>1.0</v>
+      <c r="D64" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2">
-        <v>64.0</v>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>9</v>
@@ -1465,16 +1390,16 @@
       <c r="C65" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D65" s="2">
-        <v>2.0</v>
+      <c r="D65" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2">
-        <v>65.0</v>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>10</v>
@@ -1482,16 +1407,16 @@
       <c r="C66" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D66" s="2">
-        <v>1.0</v>
+      <c r="D66" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2">
-        <v>66.0</v>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>10</v>
@@ -1499,16 +1424,16 @@
       <c r="C67" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D67" s="2">
-        <v>1.0</v>
+      <c r="D67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2">
-        <v>67.0</v>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>10</v>
@@ -1516,16 +1441,16 @@
       <c r="C68" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D68" s="2">
-        <v>1.0</v>
+      <c r="D68" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2">
-        <v>68.0</v>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>10</v>
@@ -1533,16 +1458,16 @@
       <c r="C69" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D69" s="2">
-        <v>1.0</v>
+      <c r="D69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2">
-        <v>69.0</v>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>10</v>
@@ -1550,16 +1475,16 @@
       <c r="C70" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D70" s="2">
-        <v>1.0</v>
+      <c r="D70" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2">
-        <v>70.0</v>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>10</v>
@@ -1567,16 +1492,16 @@
       <c r="C71" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D71" s="2">
-        <v>1.0</v>
+      <c r="D71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2">
-        <v>71.0</v>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>10</v>
@@ -1584,16 +1509,16 @@
       <c r="C72" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D72" s="2">
-        <v>1.0</v>
+      <c r="D72" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2">
-        <v>72.0</v>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>10</v>
@@ -1601,16 +1526,16 @@
       <c r="C73" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D73" s="2">
-        <v>1.0</v>
+      <c r="D73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2">
-        <v>73.0</v>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>10</v>
@@ -1618,16 +1543,16 @@
       <c r="C74" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="2">
-        <v>1.0</v>
+      <c r="D74" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2">
-        <v>74.0</v>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>10</v>
@@ -1635,16 +1560,16 @@
       <c r="C75" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D75" s="2">
-        <v>1.0</v>
+      <c r="D75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2">
-        <v>75.0</v>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>10</v>
@@ -1652,16 +1577,16 @@
       <c r="C76" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D76" s="2">
-        <v>1.0</v>
+      <c r="D76" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2">
-        <v>76.0</v>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>10</v>
@@ -1669,16 +1594,16 @@
       <c r="C77" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D77" s="2">
-        <v>1.0</v>
+      <c r="D77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2">
-        <v>77.0</v>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>10</v>
@@ -1686,16 +1611,16 @@
       <c r="C78" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="2">
-        <v>2.0</v>
+      <c r="D78" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2">
-        <v>78.0</v>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>10</v>
@@ -1703,16 +1628,16 @@
       <c r="C79" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="2">
-        <v>1.0</v>
+      <c r="D79" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2">
-        <v>79.0</v>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>10</v>
@@ -1720,16 +1645,16 @@
       <c r="C80" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D80" s="2">
-        <v>1.0</v>
+      <c r="D80" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2">
-        <v>80.0</v>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>10</v>
@@ -1737,16 +1662,16 @@
       <c r="C81" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D81" s="2">
-        <v>2.0</v>
+      <c r="D81" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2">
-        <v>81.0</v>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>11</v>
@@ -1754,16 +1679,16 @@
       <c r="C82" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D82" s="2">
-        <v>1.0</v>
+      <c r="D82" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2">
-        <v>82.0</v>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>11</v>
@@ -1771,16 +1696,16 @@
       <c r="C83" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D83" s="2">
-        <v>1.0</v>
+      <c r="D83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2">
-        <v>83.0</v>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>11</v>
@@ -1788,16 +1713,16 @@
       <c r="C84" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D84" s="2">
-        <v>1.0</v>
+      <c r="D84" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2">
-        <v>84.0</v>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>11</v>
@@ -1805,16 +1730,16 @@
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D85" s="2">
-        <v>1.0</v>
+      <c r="D85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2">
-        <v>85.0</v>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>11</v>
@@ -1822,16 +1747,16 @@
       <c r="C86" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D86" s="2">
-        <v>1.0</v>
+      <c r="D86" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2">
-        <v>86.0</v>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>11</v>
@@ -1839,16 +1764,16 @@
       <c r="C87" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="2">
-        <v>1.0</v>
+      <c r="D87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2">
-        <v>87.0</v>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>11</v>
@@ -1856,16 +1781,16 @@
       <c r="C88" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D88" s="2">
-        <v>1.0</v>
+      <c r="D88" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2">
-        <v>88.0</v>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>11</v>
@@ -1873,16 +1798,16 @@
       <c r="C89" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D89" s="2">
-        <v>1.0</v>
+      <c r="D89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2">
-        <v>89.0</v>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>11</v>
@@ -1890,16 +1815,16 @@
       <c r="C90" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D90" s="2">
-        <v>1.0</v>
+      <c r="D90" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2">
-        <v>90.0</v>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>11</v>
@@ -1907,16 +1832,16 @@
       <c r="C91" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D91" s="2">
-        <v>1.0</v>
+      <c r="D91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2">
-        <v>91.0</v>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>11</v>
@@ -1924,16 +1849,16 @@
       <c r="C92" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D92" s="2">
-        <v>1.0</v>
+      <c r="D92" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2">
-        <v>92.0</v>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>11</v>
@@ -1941,16 +1866,16 @@
       <c r="C93" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D93" s="2">
-        <v>1.0</v>
+      <c r="D93" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2">
-        <v>93.0</v>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>11</v>
@@ -1958,16 +1883,16 @@
       <c r="C94" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D94" s="2">
-        <v>2.0</v>
+      <c r="D94" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2">
-        <v>94.0</v>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>11</v>
@@ -1975,16 +1900,16 @@
       <c r="C95" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D95" s="2">
-        <v>1.0</v>
+      <c r="D95" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2">
-        <v>95.0</v>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>11</v>
@@ -1992,16 +1917,16 @@
       <c r="C96" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D96" s="2">
-        <v>1.0</v>
+      <c r="D96" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2">
-        <v>96.0</v>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>11</v>
@@ -2009,16 +1934,16 @@
       <c r="C97" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D97" s="2">
-        <v>5.0</v>
+      <c r="D97" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2">
-        <v>97.0</v>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>12</v>
@@ -2026,16 +1951,16 @@
       <c r="C98" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D98" s="2">
-        <v>1.0</v>
+      <c r="D98" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2">
-        <v>98.0</v>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>12</v>
@@ -2043,16 +1968,16 @@
       <c r="C99" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D99" s="2">
-        <v>1.0</v>
+      <c r="D99" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2">
-        <v>99.0</v>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>12</v>
@@ -2060,16 +1985,16 @@
       <c r="C100" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D100" s="2">
-        <v>1.0</v>
+      <c r="D100" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2">
-        <v>100.0</v>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>12</v>
@@ -2077,16 +2002,16 @@
       <c r="C101" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D101" s="2">
-        <v>1.0</v>
+      <c r="D101" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2">
-        <v>101.0</v>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>12</v>
@@ -2094,16 +2019,16 @@
       <c r="C102" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D102" s="2">
-        <v>1.0</v>
+      <c r="D102" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2">
-        <v>102.0</v>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>12</v>
@@ -2111,16 +2036,16 @@
       <c r="C103" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D103" s="2">
-        <v>1.0</v>
+      <c r="D103" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2">
-        <v>103.0</v>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>12</v>
@@ -2128,16 +2053,16 @@
       <c r="C104" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D104" s="2">
-        <v>1.0</v>
+      <c r="D104" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2">
-        <v>104.0</v>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>12</v>
@@ -2145,16 +2070,16 @@
       <c r="C105" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D105" s="2">
-        <v>1.0</v>
+      <c r="D105" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2">
-        <v>105.0</v>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>12</v>
@@ -2162,16 +2087,16 @@
       <c r="C106" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D106" s="2">
-        <v>1.0</v>
+      <c r="D106" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2">
-        <v>106.0</v>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>12</v>
@@ -2179,16 +2104,16 @@
       <c r="C107" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D107" s="2">
-        <v>1.0</v>
+      <c r="D107" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2">
-        <v>107.0</v>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>12</v>
@@ -2196,16 +2121,16 @@
       <c r="C108" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D108" s="2">
-        <v>1.0</v>
+      <c r="D108" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2">
-        <v>108.0</v>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>12</v>
@@ -2213,16 +2138,16 @@
       <c r="C109" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D109" s="2">
-        <v>1.0</v>
+      <c r="D109" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2">
-        <v>109.0</v>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>12</v>
@@ -2230,16 +2155,16 @@
       <c r="C110" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D110" s="2">
-        <v>1.0</v>
+      <c r="D110" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2">
-        <v>110.0</v>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>12</v>
@@ -2247,16 +2172,16 @@
       <c r="C111" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D111" s="2">
-        <v>1.0</v>
+      <c r="D111" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2">
-        <v>111.0</v>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>12</v>
@@ -2264,16 +2189,16 @@
       <c r="C112" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D112" s="2">
-        <v>1.0</v>
+      <c r="D112" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2">
-        <v>112.0</v>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>12</v>
@@ -2281,16 +2206,16 @@
       <c r="C113" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D113" s="2">
-        <v>2.0</v>
+      <c r="D113" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2">
-        <v>113.0</v>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>13</v>
@@ -2298,16 +2223,16 @@
       <c r="C114" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D114" s="2">
-        <v>2.0</v>
+      <c r="D114" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2">
-        <v>114.0</v>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>13</v>
@@ -2315,16 +2240,16 @@
       <c r="C115" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D115" s="2">
-        <v>1.0</v>
+      <c r="D115" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2">
-        <v>115.0</v>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>13</v>
@@ -2332,16 +2257,16 @@
       <c r="C116" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D116" s="2">
-        <v>1.0</v>
+      <c r="D116" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2">
-        <v>116.0</v>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>13</v>
@@ -2349,16 +2274,16 @@
       <c r="C117" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D117" s="2">
-        <v>1.0</v>
+      <c r="D117" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2">
-        <v>117.0</v>
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>13</v>
@@ -2366,16 +2291,16 @@
       <c r="C118" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D118" s="2">
-        <v>2.0</v>
+      <c r="D118" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2">
-        <v>118.0</v>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>13</v>
@@ -2383,16 +2308,16 @@
       <c r="C119" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D119" s="2">
-        <v>2.0</v>
+      <c r="D119" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2">
-        <v>119.0</v>
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>13</v>
@@ -2400,16 +2325,16 @@
       <c r="C120" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D120" s="2">
-        <v>1.0</v>
+      <c r="D120" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2">
-        <v>120.0</v>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>13</v>
@@ -2417,16 +2342,16 @@
       <c r="C121" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D121" s="2">
-        <v>1.0</v>
+      <c r="D121" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2">
-        <v>121.0</v>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>13</v>
@@ -2434,16 +2359,16 @@
       <c r="C122" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D122" s="2">
-        <v>1.0</v>
+      <c r="D122" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2">
-        <v>122.0</v>
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>13</v>
@@ -2451,16 +2376,16 @@
       <c r="C123" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D123" s="2">
-        <v>1.0</v>
+      <c r="D123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2">
-        <v>123.0</v>
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>13</v>
@@ -2468,16 +2393,16 @@
       <c r="C124" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D124" s="2">
-        <v>1.0</v>
+      <c r="D124" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2">
-        <v>124.0</v>
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>13</v>
@@ -2485,16 +2410,16 @@
       <c r="C125" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D125" s="2">
-        <v>1.0</v>
+      <c r="D125" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2">
-        <v>125.0</v>
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>13</v>
@@ -2502,16 +2427,16 @@
       <c r="C126" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D126" s="2">
-        <v>2.0</v>
+      <c r="D126" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2">
-        <v>126.0</v>
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>13</v>
@@ -2519,16 +2444,16 @@
       <c r="C127" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D127" s="2">
-        <v>1.0</v>
+      <c r="D127" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2">
-        <v>127.0</v>
+    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>13</v>
@@ -2536,16 +2461,16 @@
       <c r="C128" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D128" s="2">
-        <v>1.0</v>
+      <c r="D128" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2">
-        <v>128.0</v>
+    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>13</v>
@@ -2553,16 +2478,16 @@
       <c r="C129" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D129" s="2">
-        <v>5.0</v>
+      <c r="D129" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2">
-        <v>129.0</v>
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>15</v>
@@ -2570,16 +2495,16 @@
       <c r="C130" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D130" s="2">
-        <v>5.0</v>
+      <c r="D130" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2">
-        <v>130.0</v>
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>15</v>
@@ -2587,16 +2512,16 @@
       <c r="C131" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D131" s="2">
-        <v>1.0</v>
+      <c r="D131" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2">
-        <v>131.0</v>
+    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>15</v>
@@ -2604,16 +2529,16 @@
       <c r="C132" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D132" s="2">
-        <v>1.0</v>
+      <c r="D132" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2">
-        <v>132.0</v>
+    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>15</v>
@@ -2621,16 +2546,16 @@
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D133" s="2">
-        <v>1.0</v>
+      <c r="D133" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2">
-        <v>133.0</v>
+    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>15</v>
@@ -2638,16 +2563,16 @@
       <c r="C134" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D134" s="2">
-        <v>5.0</v>
+      <c r="D134" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2">
-        <v>134.0</v>
+    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>15</v>
@@ -2655,16 +2580,16 @@
       <c r="C135" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D135" s="2">
-        <v>5.0</v>
+      <c r="D135" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2">
-        <v>135.0</v>
+    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>15</v>
@@ -2672,16 +2597,16 @@
       <c r="C136" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D136" s="2">
-        <v>1.0</v>
+      <c r="D136" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2">
-        <v>136.0</v>
+    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>15</v>
@@ -2689,16 +2614,16 @@
       <c r="C137" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D137" s="2">
-        <v>1.0</v>
+      <c r="D137" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2">
-        <v>137.0</v>
+    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>15</v>
@@ -2706,16 +2631,16 @@
       <c r="C138" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D138" s="2">
-        <v>1.0</v>
+      <c r="D138" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2">
-        <v>138.0</v>
+    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>15</v>
@@ -2723,16 +2648,16 @@
       <c r="C139" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D139" s="2">
-        <v>1.0</v>
+      <c r="D139" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2">
-        <v>139.0</v>
+    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>15</v>
@@ -2740,16 +2665,16 @@
       <c r="C140" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D140" s="2">
-        <v>1.0</v>
+      <c r="D140" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2">
-        <v>140.0</v>
+    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>15</v>
@@ -2757,16 +2682,16 @@
       <c r="C141" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D141" s="2">
-        <v>1.0</v>
+      <c r="D141" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2">
-        <v>141.0</v>
+    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>15</v>
@@ -2774,16 +2699,16 @@
       <c r="C142" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D142" s="2">
-        <v>2.0</v>
+      <c r="D142" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2">
-        <v>142.0</v>
+    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>15</v>
@@ -2791,16 +2716,16 @@
       <c r="C143" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D143" s="2">
-        <v>1.0</v>
+      <c r="D143" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2">
-        <v>143.0</v>
+    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>15</v>
@@ -2808,16 +2733,16 @@
       <c r="C144" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D144" s="2">
-        <v>1.0</v>
+      <c r="D144" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2">
-        <v>144.0</v>
+    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>15</v>
@@ -2825,16 +2750,16 @@
       <c r="C145" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D145" s="2">
-        <v>5.0</v>
+      <c r="D145" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2">
-        <v>145.0</v>
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>16</v>
@@ -2842,16 +2767,16 @@
       <c r="C146" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D146" s="2">
-        <v>5.0</v>
+      <c r="D146" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2">
-        <v>146.0</v>
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>16</v>
@@ -2859,16 +2784,16 @@
       <c r="C147" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D147" s="2">
-        <v>2.0</v>
+      <c r="D147" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2">
-        <v>147.0</v>
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>16</v>
@@ -2876,16 +2801,16 @@
       <c r="C148" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D148" s="2">
-        <v>2.0</v>
+      <c r="D148" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2">
-        <v>148.0</v>
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>16</v>
@@ -2893,16 +2818,16 @@
       <c r="C149" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D149" s="2">
-        <v>2.0</v>
+      <c r="D149" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2">
-        <v>149.0</v>
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>16</v>
@@ -2910,16 +2835,16 @@
       <c r="C150" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D150" s="2">
-        <v>5.0</v>
+      <c r="D150" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2">
-        <v>150.0</v>
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>16</v>
@@ -2927,16 +2852,16 @@
       <c r="C151" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D151" s="2">
-        <v>5.0</v>
+      <c r="D151" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2">
-        <v>151.0</v>
+    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>16</v>
@@ -2944,16 +2869,16 @@
       <c r="C152" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D152" s="2">
-        <v>2.0</v>
+      <c r="D152" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2">
-        <v>152.0</v>
+    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>16</v>
@@ -2961,16 +2886,16 @@
       <c r="C153" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D153" s="2">
-        <v>1.0</v>
+      <c r="D153" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2">
-        <v>153.0</v>
+    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>16</v>
@@ -2978,16 +2903,16 @@
       <c r="C154" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D154" s="2">
-        <v>1.0</v>
+      <c r="D154" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2">
-        <v>154.0</v>
+    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>16</v>
@@ -2995,16 +2920,16 @@
       <c r="C155" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D155" s="2">
-        <v>1.0</v>
+      <c r="D155" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2">
-        <v>155.0</v>
+    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>16</v>
@@ -3012,16 +2937,16 @@
       <c r="C156" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D156" s="2">
-        <v>1.0</v>
+      <c r="D156" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2">
-        <v>156.0</v>
+    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>16</v>
@@ -3029,16 +2954,16 @@
       <c r="C157" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D157" s="2">
-        <v>2.0</v>
+      <c r="D157" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2">
-        <v>157.0</v>
+    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>16</v>
@@ -3046,16 +2971,16 @@
       <c r="C158" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D158" s="2">
-        <v>1.0</v>
+      <c r="D158" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2">
-        <v>158.0</v>
+    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>16</v>
@@ -3063,16 +2988,16 @@
       <c r="C159" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D159" s="2">
-        <v>2.0</v>
+      <c r="D159" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2">
-        <v>159.0</v>
+    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>16</v>
@@ -3080,16 +3005,16 @@
       <c r="C160" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D160" s="2">
-        <v>1.0</v>
+      <c r="D160" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2">
-        <v>160.0</v>
+    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>16</v>
@@ -3097,16 +3022,16 @@
       <c r="C161" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D161" s="2">
-        <v>5.0</v>
+      <c r="D161" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2">
-        <v>161.0</v>
+    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>17</v>
@@ -3114,16 +3039,16 @@
       <c r="C162" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D162" s="2">
-        <v>5.0</v>
+      <c r="D162" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2">
-        <v>162.0</v>
+    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>17</v>
@@ -3131,16 +3056,16 @@
       <c r="C163" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D163" s="2">
-        <v>1.0</v>
+      <c r="D163" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2">
-        <v>163.0</v>
+    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>17</v>
@@ -3148,16 +3073,16 @@
       <c r="C164" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D164" s="2">
-        <v>1.0</v>
+      <c r="D164" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2">
-        <v>164.0</v>
+    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>17</v>
@@ -3165,16 +3090,16 @@
       <c r="C165" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D165" s="2">
-        <v>1.0</v>
+      <c r="D165" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2">
-        <v>165.0</v>
+    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>17</v>
@@ -3182,16 +3107,16 @@
       <c r="C166" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D166" s="2">
-        <v>5.0</v>
+      <c r="D166" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2">
-        <v>166.0</v>
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>17</v>
@@ -3199,16 +3124,16 @@
       <c r="C167" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D167" s="2">
-        <v>5.0</v>
+      <c r="D167" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2">
-        <v>167.0</v>
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>17</v>
@@ -3216,16 +3141,16 @@
       <c r="C168" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D168" s="2">
-        <v>1.0</v>
+      <c r="D168" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2">
-        <v>168.0</v>
+    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>17</v>
@@ -3233,16 +3158,16 @@
       <c r="C169" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D169" s="2">
-        <v>1.0</v>
+      <c r="D169" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2">
-        <v>169.0</v>
+    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>17</v>
@@ -3250,16 +3175,16 @@
       <c r="C170" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D170" s="2">
-        <v>1.0</v>
+      <c r="D170" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2">
-        <v>170.0</v>
+    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>17</v>
@@ -3267,16 +3192,16 @@
       <c r="C171" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D171" s="2">
-        <v>1.0</v>
+      <c r="D171" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2">
-        <v>171.0</v>
+    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>17</v>
@@ -3284,16 +3209,16 @@
       <c r="C172" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D172" s="2">
-        <v>1.0</v>
+      <c r="D172" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2">
-        <v>172.0</v>
+    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>17</v>
@@ -3301,16 +3226,16 @@
       <c r="C173" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D173" s="2">
-        <v>1.0</v>
+      <c r="D173" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2">
-        <v>173.0</v>
+    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>17</v>
@@ -3318,16 +3243,16 @@
       <c r="C174" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D174" s="2">
-        <v>1.0</v>
+      <c r="D174" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2">
-        <v>174.0</v>
+    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>17</v>
@@ -3335,16 +3260,16 @@
       <c r="C175" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D175" s="2">
-        <v>1.0</v>
+      <c r="D175" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2">
-        <v>175.0</v>
+    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>17</v>
@@ -3352,16 +3277,16 @@
       <c r="C176" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D176" s="2">
-        <v>1.0</v>
+      <c r="D176" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2">
-        <v>176.0</v>
+    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>17</v>
@@ -3369,16 +3294,16 @@
       <c r="C177" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D177" s="2">
-        <v>1.0</v>
+      <c r="D177" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2">
-        <v>177.0</v>
+    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>18</v>
@@ -3386,16 +3311,16 @@
       <c r="C178" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D178" s="2">
-        <v>3.0</v>
+      <c r="D178" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2">
-        <v>178.0</v>
+    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>18</v>
@@ -3403,16 +3328,16 @@
       <c r="C179" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D179" s="2">
-        <v>3.0</v>
+      <c r="D179" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2">
-        <v>179.0</v>
+    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>18</v>
@@ -3420,16 +3345,16 @@
       <c r="C180" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D180" s="2">
-        <v>1.0</v>
+      <c r="D180" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2">
-        <v>180.0</v>
+    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>18</v>
@@ -3437,16 +3362,16 @@
       <c r="C181" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D181" s="2">
-        <v>3.0</v>
+      <c r="D181" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2">
-        <v>181.0</v>
+    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>18</v>
@@ -3454,16 +3379,16 @@
       <c r="C182" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D182" s="2">
-        <v>3.0</v>
+      <c r="D182" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2">
-        <v>182.0</v>
+    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>18</v>
@@ -3471,16 +3396,16 @@
       <c r="C183" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D183" s="2">
-        <v>3.0</v>
+      <c r="D183" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2">
-        <v>183.0</v>
+    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>18</v>
@@ -3488,16 +3413,16 @@
       <c r="C184" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D184" s="2">
-        <v>3.0</v>
+      <c r="D184" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2">
-        <v>184.0</v>
+    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>18</v>
@@ -3505,16 +3430,16 @@
       <c r="C185" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D185" s="2">
-        <v>3.0</v>
+      <c r="D185" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2">
-        <v>185.0</v>
+    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>18</v>
@@ -3522,16 +3447,16 @@
       <c r="C186" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D186" s="2">
-        <v>3.0</v>
+      <c r="D186" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2">
-        <v>186.0</v>
+    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>18</v>
@@ -3539,16 +3464,16 @@
       <c r="C187" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D187" s="2">
-        <v>3.0</v>
+      <c r="D187" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2">
-        <v>187.0</v>
+    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>18</v>
@@ -3556,16 +3481,16 @@
       <c r="C188" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D188" s="2">
-        <v>3.0</v>
+      <c r="D188" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2">
-        <v>188.0</v>
+    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>18</v>
@@ -3573,16 +3498,16 @@
       <c r="C189" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D189" s="2">
-        <v>1.0</v>
+      <c r="D189" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2">
-        <v>189.0</v>
+    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>18</v>
@@ -3590,16 +3515,16 @@
       <c r="C190" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D190" s="2">
-        <v>1.0</v>
+      <c r="D190" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2">
-        <v>190.0</v>
+    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>18</v>
@@ -3607,16 +3532,16 @@
       <c r="C191" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D191" s="2">
-        <v>3.0</v>
+      <c r="D191" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2">
-        <v>191.0</v>
+    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>18</v>
@@ -3624,16 +3549,16 @@
       <c r="C192" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D192" s="2">
-        <v>2.0</v>
+      <c r="D192" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2">
-        <v>192.0</v>
+    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>18</v>
@@ -3641,16 +3566,16 @@
       <c r="C193" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D193" s="2">
-        <v>5.0</v>
+      <c r="D193" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2">
-        <v>193.0</v>
+    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>19</v>
@@ -3658,16 +3583,16 @@
       <c r="C194" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D194" s="2">
-        <v>3.0</v>
+      <c r="D194" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2">
-        <v>194.0</v>
+    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>19</v>
@@ -3675,16 +3600,16 @@
       <c r="C195" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D195" s="2">
-        <v>3.0</v>
+      <c r="D195" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2">
-        <v>195.0</v>
+    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>19</v>
@@ -3692,16 +3617,16 @@
       <c r="C196" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D196" s="2">
-        <v>1.0</v>
+      <c r="D196" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2">
-        <v>196.0</v>
+    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>19</v>
@@ -3709,16 +3634,16 @@
       <c r="C197" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D197" s="2">
-        <v>3.0</v>
+      <c r="D197" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2">
-        <v>197.0</v>
+    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>19</v>
@@ -3726,16 +3651,16 @@
       <c r="C198" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D198" s="2">
-        <v>3.0</v>
+      <c r="D198" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2">
-        <v>198.0</v>
+    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>19</v>
@@ -3743,16 +3668,16 @@
       <c r="C199" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D199" s="2">
-        <v>3.0</v>
+      <c r="D199" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2">
-        <v>199.0</v>
+    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>19</v>
@@ -3760,16 +3685,16 @@
       <c r="C200" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D200" s="2">
-        <v>3.0</v>
+      <c r="D200" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2">
-        <v>200.0</v>
+    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>19</v>
@@ -3777,16 +3702,16 @@
       <c r="C201" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D201" s="2">
-        <v>3.0</v>
+      <c r="D201" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2">
-        <v>201.0</v>
+    <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>19</v>
@@ -3794,16 +3719,16 @@
       <c r="C202" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D202" s="2">
-        <v>3.0</v>
+      <c r="D202" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2">
-        <v>202.0</v>
+    <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>19</v>
@@ -3811,16 +3736,16 @@
       <c r="C203" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D203" s="2">
-        <v>3.0</v>
+      <c r="D203" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2">
-        <v>203.0</v>
+    <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>19</v>
@@ -3828,16 +3753,16 @@
       <c r="C204" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D204" s="2">
-        <v>3.0</v>
+      <c r="D204" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2">
-        <v>204.0</v>
+    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>19</v>
@@ -3845,16 +3770,16 @@
       <c r="C205" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D205" s="3">
-        <v>46054.0</v>
+      <c r="D205" s="3" t="n">
+        <v>46054</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2">
-        <v>205.0</v>
+    <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>19</v>
@@ -3862,16 +3787,16 @@
       <c r="C206" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D206" s="2">
-        <v>1.0</v>
+      <c r="D206" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2">
-        <v>206.0</v>
+    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>19</v>
@@ -3879,16 +3804,16 @@
       <c r="C207" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D207" s="2">
-        <v>3.0</v>
+      <c r="D207" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2">
-        <v>207.0</v>
+    <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>19</v>
@@ -3896,16 +3821,16 @@
       <c r="C208" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D208" s="2">
-        <v>1.0</v>
+      <c r="D208" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2">
-        <v>208.0</v>
+    <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>19</v>
@@ -3913,16 +3838,16 @@
       <c r="C209" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D209" s="2">
-        <v>1.0</v>
+      <c r="D209" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2">
-        <v>209.0</v>
+    <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>20</v>
@@ -3935,9 +3860,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2">
-        <v>210.0</v>
+    <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>20</v>
@@ -3945,16 +3870,16 @@
       <c r="C211" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D211" s="2">
-        <v>2.0</v>
+      <c r="D211" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2">
-        <v>211.0</v>
+    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>20</v>
@@ -3962,16 +3887,16 @@
       <c r="C212" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D212" s="2">
-        <v>2.0</v>
+      <c r="D212" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2">
-        <v>212.0</v>
+    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>20</v>
@@ -3979,16 +3904,16 @@
       <c r="C213" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D213" s="2">
-        <v>2.0</v>
+      <c r="D213" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2">
-        <v>213.0</v>
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>20</v>
@@ -4001,9 +3926,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2">
-        <v>214.0</v>
+    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>20</v>
@@ -4016,9 +3941,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2">
-        <v>215.0</v>
+    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>20</v>
@@ -4031,9 +3956,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2">
-        <v>216.0</v>
+    <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2" t="n">
+        <v>216</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>20</v>
@@ -4041,16 +3966,16 @@
       <c r="C217" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D217" s="2">
-        <v>5.0</v>
+      <c r="D217" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2">
-        <v>217.0</v>
+    <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="2" t="n">
+        <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>20</v>
@@ -4058,16 +3983,16 @@
       <c r="C218" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D218" s="2">
-        <v>3.0</v>
+      <c r="D218" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2">
-        <v>218.0</v>
+    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="2" t="n">
+        <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>20</v>
@@ -4075,16 +4000,16 @@
       <c r="C219" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D219" s="2">
-        <v>3.0</v>
+      <c r="D219" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2">
-        <v>219.0</v>
+    <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>20</v>
@@ -4092,16 +4017,16 @@
       <c r="C220" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D220" s="2">
-        <v>2.0</v>
+      <c r="D220" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2">
-        <v>220.0</v>
+    <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="2" t="n">
+        <v>220</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>20</v>
@@ -4109,16 +4034,16 @@
       <c r="C221" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D221" s="2">
-        <v>2.0</v>
+      <c r="D221" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2">
-        <v>221.0</v>
+    <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>20</v>
@@ -4126,16 +4051,16 @@
       <c r="C222" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D222" s="2">
-        <v>6.0</v>
+      <c r="D222" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2">
-        <v>222.0</v>
+    <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="n">
+        <v>222</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>20</v>
@@ -4143,16 +4068,16 @@
       <c r="C223" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D223" s="2">
-        <v>2.0</v>
+      <c r="D223" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2">
-        <v>223.0</v>
+    <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="2" t="n">
+        <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>20</v>
@@ -4160,16 +4085,16 @@
       <c r="C224" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D224" s="2">
-        <v>2.0</v>
+      <c r="D224" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2">
-        <v>224.0</v>
+    <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2" t="n">
+        <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>20</v>
@@ -4177,16 +4102,16 @@
       <c r="C225" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D225" s="2">
-        <v>6.0</v>
+      <c r="D225" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2">
-        <v>225.0</v>
+    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>21</v>
@@ -4199,9 +4124,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2">
-        <v>226.0</v>
+    <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="2" t="n">
+        <v>226</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>21</v>
@@ -4209,16 +4134,16 @@
       <c r="C227" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D227" s="2">
-        <v>3.0</v>
+      <c r="D227" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2">
-        <v>227.0</v>
+    <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>21</v>
@@ -4226,16 +4151,16 @@
       <c r="C228" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D228" s="2">
-        <v>2.0</v>
+      <c r="D228" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2">
-        <v>228.0</v>
+    <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="2" t="n">
+        <v>228</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>21</v>
@@ -4243,16 +4168,16 @@
       <c r="C229" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D229" s="2">
-        <v>3.0</v>
+      <c r="D229" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2">
-        <v>229.0</v>
+    <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="2" t="n">
+        <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>21</v>
@@ -4265,9 +4190,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2">
-        <v>230.0</v>
+    <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="2" t="n">
+        <v>230</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>21</v>
@@ -4280,9 +4205,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2">
-        <v>231.0</v>
+    <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="2" t="n">
+        <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>21</v>
@@ -4295,9 +4220,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2">
-        <v>232.0</v>
+    <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="2" t="n">
+        <v>232</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>21</v>
@@ -4305,16 +4230,16 @@
       <c r="C233" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D233" s="2">
-        <v>3.0</v>
+      <c r="D233" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2">
-        <v>233.0</v>
+    <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="2" t="n">
+        <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>21</v>
@@ -4322,16 +4247,16 @@
       <c r="C234" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D234" s="2">
-        <v>3.0</v>
+      <c r="D234" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2">
-        <v>234.0</v>
+    <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="2" t="n">
+        <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>21</v>
@@ -4339,16 +4264,16 @@
       <c r="C235" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D235" s="2">
-        <v>3.0</v>
+      <c r="D235" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2">
-        <v>235.0</v>
+    <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>21</v>
@@ -4356,16 +4281,16 @@
       <c r="C236" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D236" s="2">
-        <v>2.0</v>
+      <c r="D236" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2">
-        <v>236.0</v>
+    <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="2" t="n">
+        <v>236</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>21</v>
@@ -4373,16 +4298,16 @@
       <c r="C237" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D237" s="2">
-        <v>2.0</v>
+      <c r="D237" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2">
-        <v>237.0</v>
+    <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>21</v>
@@ -4390,16 +4315,16 @@
       <c r="C238" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D238" s="2">
-        <v>6.0</v>
+      <c r="D238" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2">
-        <v>238.0</v>
+    <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>21</v>
@@ -4407,16 +4332,16 @@
       <c r="C239" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D239" s="2">
-        <v>3.0</v>
+      <c r="D239" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2">
-        <v>239.0</v>
+    <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>21</v>
@@ -4424,16 +4349,16 @@
       <c r="C240" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D240" s="2">
-        <v>2.0</v>
+      <c r="D240" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2">
-        <v>240.0</v>
+    <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>21</v>
@@ -4441,16 +4366,16 @@
       <c r="C241" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D241" s="2">
-        <v>6.0</v>
+      <c r="D241" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2">
-        <v>241.0</v>
+    <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="2" t="n">
+        <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>22</v>
@@ -4458,16 +4383,16 @@
       <c r="C242" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D242" s="2">
-        <v>4.0</v>
+      <c r="D242" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2">
-        <v>242.0</v>
+    <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="2" t="n">
+        <v>242</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>22</v>
@@ -4475,16 +4400,16 @@
       <c r="C243" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D243" s="2">
-        <v>4.0</v>
+      <c r="D243" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2">
-        <v>243.0</v>
+    <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>22</v>
@@ -4492,16 +4417,16 @@
       <c r="C244" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D244" s="2">
-        <v>4.0</v>
+      <c r="D244" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2">
-        <v>244.0</v>
+    <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>22</v>
@@ -4509,16 +4434,16 @@
       <c r="C245" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D245" s="2">
-        <v>4.0</v>
+      <c r="D245" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2">
-        <v>245.0</v>
+    <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>22</v>
@@ -4526,16 +4451,16 @@
       <c r="C246" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D246" s="2">
-        <v>4.0</v>
+      <c r="D246" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2">
-        <v>246.0</v>
+    <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>22</v>
@@ -4543,16 +4468,16 @@
       <c r="C247" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D247" s="2">
-        <v>4.0</v>
+      <c r="D247" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2">
-        <v>247.0</v>
+    <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>22</v>
@@ -4560,16 +4485,16 @@
       <c r="C248" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D248" s="2">
-        <v>4.0</v>
+      <c r="D248" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2">
-        <v>248.0</v>
+    <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>22</v>
@@ -4577,16 +4502,16 @@
       <c r="C249" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D249" s="2">
-        <v>4.0</v>
+      <c r="D249" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2">
-        <v>249.0</v>
+    <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>22</v>
@@ -4594,16 +4519,16 @@
       <c r="C250" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D250" s="2">
-        <v>4.0</v>
+      <c r="D250" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2">
-        <v>250.0</v>
+    <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>22</v>
@@ -4611,16 +4536,16 @@
       <c r="C251" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D251" s="2">
-        <v>4.0</v>
+      <c r="D251" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2">
-        <v>251.0</v>
+    <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>22</v>
@@ -4628,16 +4553,16 @@
       <c r="C252" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D252" s="2">
-        <v>4.0</v>
+      <c r="D252" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2">
-        <v>252.0</v>
+    <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>22</v>
@@ -4645,16 +4570,16 @@
       <c r="C253" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D253" s="2">
-        <v>4.0</v>
+      <c r="D253" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2">
-        <v>253.0</v>
+    <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>22</v>
@@ -4662,16 +4587,16 @@
       <c r="C254" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D254" s="2">
-        <v>7.0</v>
+      <c r="D254" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2">
-        <v>254.0</v>
+    <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>22</v>
@@ -4679,16 +4604,16 @@
       <c r="C255" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D255" s="2">
-        <v>4.0</v>
+      <c r="D255" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2">
-        <v>255.0</v>
+    <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>22</v>
@@ -4696,16 +4621,16 @@
       <c r="C256" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D256" s="2">
-        <v>4.0</v>
+      <c r="D256" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2">
-        <v>256.0</v>
+    <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>22</v>
@@ -4713,14 +4638,20 @@
       <c r="C257" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D257" s="2">
-        <v>7.0</v>
+      <c r="D257" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>